--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484731_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484731_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.517799999999999</v>
+        <v>8.7758</v>
       </c>
       <c r="E2" t="n">
-        <v>7.2815</v>
+        <v>6.9892</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2363</v>
+        <v>1.7865</v>
       </c>
       <c r="G2" t="n">
         <v>6.3105</v>
@@ -610,13 +610,13 @@
         <v>1.1322</v>
       </c>
       <c r="S2" t="n">
-        <v>1.1699</v>
+        <v>0.4278</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1147</v>
+        <v>-0.407</v>
       </c>
       <c r="U2" t="n">
-        <v>1.2845</v>
+        <v>0.8348</v>
       </c>
       <c r="V2" t="n">
         <v>2.7922</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>8.041700000000001</v>
+        <v>8.2895</v>
       </c>
       <c r="E3" t="n">
-        <v>7.9568</v>
+        <v>8.1517</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0849</v>
+        <v>0.1378</v>
       </c>
       <c r="G3" t="n">
         <v>4.6017</v>
@@ -688,13 +688,13 @@
         <v>2.4531</v>
       </c>
       <c r="S3" t="n">
-        <v>0.08169999999999999</v>
+        <v>0.3295</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0276</v>
+        <v>0.2224</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0542</v>
+        <v>0.1071</v>
       </c>
       <c r="V3" t="n">
         <v>3.7356</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.2961</v>
+        <v>5.735</v>
       </c>
       <c r="E4" t="n">
-        <v>5.0871</v>
+        <v>5.3407</v>
       </c>
       <c r="F4" t="n">
-        <v>0.209</v>
+        <v>0.3942</v>
       </c>
       <c r="G4" t="n">
         <v>3.8417</v>
@@ -766,13 +766,13 @@
         <v>2.4531</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2657</v>
+        <v>0.7045</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2874</v>
+        <v>0.5411</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0217</v>
+        <v>0.1635</v>
       </c>
       <c r="V4" t="n">
         <v>0.6226</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>H. RODRIGUEZ GUTIERREZ</t>
+          <t>D. SARRIAS SANCHEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.1119</v>
+        <v>2.2225</v>
       </c>
       <c r="E5" t="n">
-        <v>3.3364</v>
+        <v>0.7299</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.2244</v>
+        <v>1.4926</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.7184</v>
+        <v>-1.2632</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1667</v>
+        <v>-1.9408</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5517</v>
+        <v>0.6776</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9827</v>
+        <v>-0.1733</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7771</v>
+        <v>-1.0456</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2057</v>
+        <v>0.8723</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.7012</v>
+        <v>-1.0899</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.9438</v>
+        <v>-0.8953</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.7574</v>
+        <v>-0.1946</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1887</v>
+        <v>2.2644</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9435</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1322</v>
+        <v>2.2644</v>
       </c>
       <c r="S5" t="n">
-        <v>3.6417</v>
+        <v>-0.0239</v>
       </c>
       <c r="T5" t="n">
-        <v>3.2972</v>
+        <v>-0.342</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3445</v>
+        <v>0.3181</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.2452</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.2452</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. SARRIAS SANCHEZ</t>
+          <t>H. RODRIGUEZ GUTIERREZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.8508</v>
+        <v>1.293</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4376</v>
+        <v>1.5439</v>
       </c>
       <c r="F6" t="n">
-        <v>1.4132</v>
+        <v>-0.2509</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.2632</v>
+        <v>-0.7184</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.9408</v>
+        <v>-0.1667</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6776</v>
+        <v>-0.5517</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.1733</v>
+        <v>0.9827</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.0456</v>
+        <v>0.7771</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8723</v>
+        <v>0.2057</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.0899</v>
+        <v>-1.7012</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.8953</v>
+        <v>-0.9438</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.1946</v>
+        <v>-0.7574</v>
       </c>
       <c r="P6" t="n">
-        <v>2.2644</v>
+        <v>0.1887</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.9435</v>
       </c>
       <c r="R6" t="n">
-        <v>2.2644</v>
+        <v>1.1322</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3956</v>
+        <v>1.8228</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6343</v>
+        <v>1.5047</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2387</v>
+        <v>0.3181</v>
       </c>
       <c r="V6" t="n">
-        <v>1.2452</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2452</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2404</v>
+        <v>1.0191</v>
       </c>
       <c r="E7" t="n">
-        <v>4.093</v>
+        <v>3.8982</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.8527</v>
+        <v>-2.8791</v>
       </c>
       <c r="G7" t="n">
         <v>2.7754</v>
@@ -1000,13 +1000,13 @@
         <v>0.1887</v>
       </c>
       <c r="S7" t="n">
-        <v>0.465</v>
+        <v>0.2437</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4732</v>
+        <v>0.2783</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.008200000000000001</v>
+        <v>-0.0347</v>
       </c>
       <c r="V7" t="n">
         <v>-1.2452</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6322</v>
+        <v>0.7826</v>
       </c>
       <c r="E9" t="n">
-        <v>1.0049</v>
+        <v>1.1024</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3727</v>
+        <v>-0.3198</v>
       </c>
       <c r="G9" t="n">
         <v>0.555</v>
@@ -1156,13 +1156,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2246</v>
+        <v>-0.0742</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1176</v>
+        <v>-0.0201</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.107</v>
+        <v>-0.0541</v>
       </c>
       <c r="V9" t="n">
         <v>0.3018</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.6539</v>
+        <v>-0.7333</v>
       </c>
       <c r="E11" t="n">
         <v>-0.9435</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2896</v>
+        <v>0.2102</v>
       </c>
       <c r="G11" t="n">
         <v>0.0485</v>
@@ -1312,13 +1312,13 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0.241</v>
+        <v>0.1617</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>0.241</v>
+        <v>0.1617</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.1751</v>
+        <v>-0.9925</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.4074</v>
+        <v>-0.2512</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.7677</v>
+        <v>-0.7413</v>
       </c>
       <c r="G12" t="n">
         <v>-0.7712</v>
@@ -1390,13 +1390,13 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2187</v>
+        <v>0.4013</v>
       </c>
       <c r="T12" t="n">
-        <v>0.201</v>
+        <v>0.3573</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0176</v>
+        <v>0.0441</v>
       </c>
       <c r="V12" t="n">
         <v>-0.6226</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.8769</v>
+        <v>-1.8059</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.1146</v>
+        <v>-1.0172</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.7623</v>
+        <v>-0.7887</v>
       </c>
       <c r="G13" t="n">
         <v>-1.5871</v>
@@ -1468,13 +1468,13 @@
         <v>0.9435</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2898</v>
+        <v>-0.2188</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0465</v>
+        <v>0.051</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2433</v>
+        <v>-0.2698</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-4.9225</v>
+        <v>-4.1204</v>
       </c>
       <c r="E14" t="n">
-        <v>-3.0665</v>
+        <v>-2.4231</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.856</v>
+        <v>-1.6973</v>
       </c>
       <c r="G14" t="n">
         <v>0.0032</v>
@@ -1546,13 +1546,13 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0935</v>
+        <v>0.8956</v>
       </c>
       <c r="T14" t="n">
-        <v>0.037</v>
+        <v>0.6804</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0565</v>
+        <v>0.2152</v>
       </c>
       <c r="V14" t="n">
         <v>-1.2452</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-6.8506</v>
+        <v>-5.9594</v>
       </c>
       <c r="E15" t="n">
-        <v>-5.4314</v>
+        <v>-4.5932</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.4191</v>
+        <v>-1.3662</v>
       </c>
       <c r="G15" t="n">
         <v>-4.094</v>
@@ -1624,13 +1624,13 @@
         <v>1.6983</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.3791</v>
+        <v>0.512</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.5508999999999999</v>
+        <v>0.2874</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1717</v>
+        <v>0.2246</v>
       </c>
       <c r="V15" t="n">
         <v>-1.2452</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>15.7628</v>
+        <v>16.0569</v>
       </c>
       <c r="E16" t="n">
-        <v>19.7848</v>
+        <v>20.0787</v>
       </c>
       <c r="F16" t="n">
-        <v>-4.0219</v>
+        <v>-4.022</v>
       </c>
       <c r="G16" t="n">
         <v>11.253</v>
@@ -1702,19 +1702,19 @@
         <v>12.2655</v>
       </c>
       <c r="S16" t="n">
-        <v>4.8881</v>
+        <v>5.182</v>
       </c>
       <c r="T16" t="n">
-        <v>2.8594</v>
+        <v>3.1535</v>
       </c>
       <c r="U16" t="n">
-        <v>2.0285</v>
+        <v>2.0286</v>
       </c>
       <c r="V16" t="n">
         <v>4.339199999999998</v>
       </c>
       <c r="W16" t="n">
-        <v>9.942599999999999</v>
+        <v>9.942600000000001</v>
       </c>
       <c r="X16" t="n">
         <v>-5.603400000000001</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.6334</v>
+        <v>1.5328</v>
       </c>
       <c r="E17" t="n">
-        <v>3.6916</v>
+        <v>2.6198</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.0582</v>
+        <v>-1.087</v>
       </c>
       <c r="G17" t="n">
         <v>0.7688</v>
@@ -1780,13 +1780,13 @@
         <v>0.9435</v>
       </c>
       <c r="S17" t="n">
-        <v>1.8646</v>
+        <v>0.7641</v>
       </c>
       <c r="T17" t="n">
-        <v>1.7382</v>
+        <v>0.6664</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1264</v>
+        <v>0.09760000000000001</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1665</v>
+        <v>0.0367</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.1341</v>
+        <v>-0.0367</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.0324</v>
+        <v>0.07340000000000001</v>
       </c>
       <c r="G20" t="n">
         <v>-0.0607</v>
@@ -2014,13 +2014,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1058</v>
+        <v>0.0974</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1764</v>
+        <v>-0.0789</v>
       </c>
       <c r="U20" t="n">
-        <v>0.07049999999999999</v>
+        <v>0.1764</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.8121</v>
+        <v>-0.0688</v>
       </c>
       <c r="E21" t="n">
-        <v>1.3399</v>
+        <v>1.5347</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.152</v>
+        <v>-1.6036</v>
       </c>
       <c r="G21" t="n">
         <v>-1.3031</v>
@@ -2092,13 +2092,13 @@
         <v>1.3209</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.1316</v>
+        <v>-0.3883</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.458</v>
+        <v>-0.2631</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6737</v>
+        <v>-0.1252</v>
       </c>
       <c r="V21" t="n">
         <v>1.2452</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.8234</v>
+        <v>-0.5924</v>
       </c>
       <c r="E22" t="n">
         <v>2.2756</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.099</v>
+        <v>-2.868</v>
       </c>
       <c r="G22" t="n">
         <v>-2.053</v>
@@ -2170,13 +2170,13 @@
         <v>2.4531</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6008</v>
+        <v>-0.3698</v>
       </c>
       <c r="T22" t="n">
         <v>-0.6902</v>
       </c>
       <c r="U22" t="n">
-        <v>0.08939999999999999</v>
+        <v>0.3204</v>
       </c>
       <c r="V22" t="n">
         <v>0.3208</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>P. GOMEZ FURONES</t>
+          <t>A. DOMINGUEZ CARRAL</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.8587</v>
+        <v>-0.7959000000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.7837</v>
+        <v>3.6426</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.0751</v>
+        <v>-4.4385</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.8887</v>
+        <v>2.6946</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1722</v>
+        <v>3.4113</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.0609</v>
+        <v>-0.7168</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.6073</v>
+        <v>4.8453</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0423</v>
+        <v>4.6963</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.6496</v>
+        <v>0.1489</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.2814</v>
+        <v>-2.1507</v>
       </c>
       <c r="N23" t="n">
-        <v>0.1299</v>
+        <v>-1.285</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.4113</v>
+        <v>-0.8657</v>
       </c>
       <c r="P23" t="n">
-        <v>0.1887</v>
+        <v>0.3774</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-1.887</v>
       </c>
       <c r="R23" t="n">
-        <v>0.1887</v>
+        <v>2.2644</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1587</v>
+        <v>-0.1323</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1764</v>
+        <v>0.0617</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0176</v>
+        <v>-0.194</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-3.7356</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>0.6226</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-4.3582</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>I. HORRACH SANCHEZ</t>
+          <t>P. GOMEZ FURONES</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,58 +2281,58 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.2489</v>
+        <v>-0.8323</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.7373</v>
+        <v>-0.7837</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.5115</v>
+        <v>-0.0486</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.5058</v>
+        <v>-0.8887</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.09</v>
+        <v>0.1722</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.4158</v>
+        <v>-1.0609</v>
       </c>
       <c r="J24" t="n">
-        <v>0.1227</v>
+        <v>-0.6073</v>
       </c>
       <c r="K24" t="n">
-        <v>0.1057</v>
+        <v>0.0423</v>
       </c>
       <c r="L24" t="n">
-        <v>0.017</v>
+        <v>-0.6496</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.6284999999999999</v>
+        <v>-0.2814</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.1956</v>
+        <v>0.1299</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.4329</v>
+        <v>-0.4113</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.3774</v>
+        <v>0.1887</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.9435</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0.5661</v>
+        <v>0.1887</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.3656</v>
+        <v>-0.1323</v>
       </c>
       <c r="T24" t="n">
-        <v>0.0835</v>
+        <v>-0.1764</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4491</v>
+        <v>0.0441</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2347,7 +2347,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A. DOMINGUEZ CARRAL</t>
+          <t>J. ARTIGUES DANOBEITIA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2359,73 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.3661</v>
+        <v>-0.8758</v>
       </c>
       <c r="E25" t="n">
-        <v>3.2528</v>
+        <v>-1.0304</v>
       </c>
       <c r="F25" t="n">
-        <v>-4.619</v>
+        <v>0.1546</v>
       </c>
       <c r="G25" t="n">
-        <v>2.6946</v>
+        <v>-0.8724</v>
       </c>
       <c r="H25" t="n">
-        <v>3.4113</v>
+        <v>-0.7575</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.7168</v>
+        <v>-0.1149</v>
       </c>
       <c r="J25" t="n">
-        <v>4.8453</v>
+        <v>-0.4224</v>
       </c>
       <c r="K25" t="n">
-        <v>4.6963</v>
+        <v>-0.4805</v>
       </c>
       <c r="L25" t="n">
-        <v>0.1489</v>
+        <v>0.0582</v>
       </c>
       <c r="M25" t="n">
-        <v>-2.1507</v>
+        <v>-0.4501</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.285</v>
+        <v>-0.277</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.8657</v>
+        <v>-0.173</v>
       </c>
       <c r="P25" t="n">
         <v>0.3774</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1.887</v>
+        <v>-0.9435</v>
       </c>
       <c r="R25" t="n">
-        <v>2.2644</v>
+        <v>1.3209</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.7025</v>
+        <v>-0.0789</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.3281</v>
+        <v>0.3355</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.3744</v>
+        <v>-0.4144</v>
       </c>
       <c r="V25" t="n">
-        <v>-3.7356</v>
+        <v>-0.3018</v>
       </c>
       <c r="W25" t="n">
-        <v>0.6226</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-4.3582</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>V. CARLES TEJEDO</t>
+          <t>I. HORRACH SANCHEZ</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,58 +2437,58 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-1.4637</v>
+        <v>-0.9157</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.5456</v>
+        <v>-0.6399</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0819</v>
+        <v>-0.2758</v>
       </c>
       <c r="G26" t="n">
-        <v>-1.359</v>
+        <v>-0.5058</v>
       </c>
       <c r="H26" t="n">
-        <v>-1.3375</v>
+        <v>-0.09</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.0216</v>
+        <v>-0.4158</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.2864</v>
+        <v>0.1227</v>
       </c>
       <c r="K26" t="n">
-        <v>-1.109</v>
+        <v>0.1057</v>
       </c>
       <c r="L26" t="n">
-        <v>0.8226</v>
+        <v>0.017</v>
       </c>
       <c r="M26" t="n">
-        <v>-1.0727</v>
+        <v>-0.6284999999999999</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.2285</v>
+        <v>-0.1956</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.8442</v>
+        <v>-0.4329</v>
       </c>
       <c r="P26" t="n">
-        <v>-0.1887</v>
+        <v>-0.3774</v>
       </c>
       <c r="Q26" t="n">
-        <v>-1.887</v>
+        <v>-0.9435</v>
       </c>
       <c r="R26" t="n">
-        <v>1.6983</v>
+        <v>0.5661</v>
       </c>
       <c r="S26" t="n">
-        <v>0.08400000000000001</v>
+        <v>-0.0325</v>
       </c>
       <c r="T26" t="n">
-        <v>0.6278</v>
+        <v>0.1809</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.5437</v>
+        <v>-0.2134</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -2503,7 +2503,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>J. ARTIGUES DANOBEITIA</t>
+          <t>V. CARLES TEJEDO</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2515,67 +2515,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-1.5987</v>
+        <v>-1.3699</v>
       </c>
       <c r="E27" t="n">
-        <v>-1.5175</v>
+        <v>-1.7404</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.08110000000000001</v>
+        <v>0.3705</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.8724</v>
+        <v>-1.359</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.7575</v>
+        <v>-1.3375</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.1149</v>
+        <v>-0.0216</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.4224</v>
+        <v>-0.2864</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.4805</v>
+        <v>-1.109</v>
       </c>
       <c r="L27" t="n">
-        <v>0.0582</v>
+        <v>0.8226</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.4501</v>
+        <v>-1.0727</v>
       </c>
       <c r="N27" t="n">
-        <v>-0.277</v>
+        <v>-0.2285</v>
       </c>
       <c r="O27" t="n">
-        <v>-0.173</v>
+        <v>-0.8442</v>
       </c>
       <c r="P27" t="n">
-        <v>0.3774</v>
+        <v>-0.1887</v>
       </c>
       <c r="Q27" t="n">
-        <v>-0.9435</v>
+        <v>-1.887</v>
       </c>
       <c r="R27" t="n">
-        <v>1.3209</v>
+        <v>1.6983</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.8018</v>
+        <v>0.1778</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.1517</v>
+        <v>0.4329</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.6501</v>
+        <v>-0.2551</v>
       </c>
       <c r="V27" t="n">
-        <v>-0.3018</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
         <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>-0.3018</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-3.1784</v>
+        <v>-3.0796</v>
       </c>
       <c r="E28" t="n">
         <v>-0.1982</v>
       </c>
       <c r="F28" t="n">
-        <v>-2.9802</v>
+        <v>-2.8814</v>
       </c>
       <c r="G28" t="n">
         <v>-2.972</v>
@@ -2638,13 +2638,13 @@
         <v>2.2644</v>
       </c>
       <c r="S28" t="n">
-        <v>-0.5837</v>
+        <v>-0.485</v>
       </c>
       <c r="T28" t="n">
         <v>-0.749</v>
       </c>
       <c r="U28" t="n">
-        <v>0.1653</v>
+        <v>0.264</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -2671,13 +2671,13 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>-3.8504</v>
+        <v>-3.3428</v>
       </c>
       <c r="E29" t="n">
-        <v>-2.8291</v>
+        <v>-2.6343</v>
       </c>
       <c r="F29" t="n">
-        <v>-1.0213</v>
+        <v>-0.7086</v>
       </c>
       <c r="G29" t="n">
         <v>-3.1579</v>
@@ -2716,13 +2716,13 @@
         <v>1.5096</v>
       </c>
       <c r="S29" t="n">
-        <v>-1.5796</v>
+        <v>-1.072</v>
       </c>
       <c r="T29" t="n">
-        <v>-1.0582</v>
+        <v>-0.8633</v>
       </c>
       <c r="U29" t="n">
-        <v>-0.5214</v>
+        <v>-0.2087</v>
       </c>
       <c r="V29" t="n">
         <v>-0.6226</v>
@@ -2749,13 +2749,13 @@
         <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>-4.914</v>
+        <v>-4.6481</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.6771</v>
+        <v>-0.7745</v>
       </c>
       <c r="F30" t="n">
-        <v>-4.2369</v>
+        <v>-3.8736</v>
       </c>
       <c r="G30" t="n">
         <v>-3.4283</v>
@@ -2794,13 +2794,13 @@
         <v>2.4531</v>
       </c>
       <c r="S30" t="n">
-        <v>-0.8065</v>
+        <v>-0.5407</v>
       </c>
       <c r="T30" t="n">
-        <v>-0.6902</v>
+        <v>-0.7876</v>
       </c>
       <c r="U30" t="n">
-        <v>-0.1163</v>
+        <v>0.2469</v>
       </c>
       <c r="V30" t="n">
         <v>-1.2452</v>
@@ -2827,13 +2827,13 @@
         <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>-15.7627</v>
+        <v>-13.067</v>
       </c>
       <c r="E31" t="n">
-        <v>4.022099999999999</v>
+        <v>4.119399999999999</v>
       </c>
       <c r="F31" t="n">
-        <v>-19.7848</v>
+        <v>-17.1866</v>
       </c>
       <c r="G31" t="n">
         <v>-11.2527</v>
@@ -2863,7 +2863,7 @@
         <v>-16.8833</v>
       </c>
       <c r="P31" t="n">
-        <v>4.717499999999999</v>
+        <v>4.717500000000001</v>
       </c>
       <c r="Q31" t="n">
         <v>-12.2655</v>
@@ -2872,13 +2872,13 @@
         <v>16.983</v>
       </c>
       <c r="S31" t="n">
-        <v>-4.888</v>
+        <v>-2.1925</v>
       </c>
       <c r="T31" t="n">
-        <v>-2.0287</v>
+        <v>-1.9311</v>
       </c>
       <c r="U31" t="n">
-        <v>-2.8595</v>
+        <v>-0.2614</v>
       </c>
       <c r="V31" t="n">
         <v>-4.3392</v>
